--- a/data-raw/desc_fontes_de_recursos.xlsx
+++ b/data-raw/desc_fontes_de_recursos.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29324"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m753205\Desktop\99 TABELAS APOIO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_50E8B19B325462AB430540D226A1CE6240D7173E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{918EBDB3-B38F-4D91-B10C-BC2CD208FFA2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19350" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19350" windowHeight="7965"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$C$100</definedName>
     <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="221">
   <si>
     <t>CODIGO</t>
   </si>
@@ -634,13 +633,85 @@
   </si>
   <si>
     <t>RECURSOS PREVISTOS NO ART. 5º, INCISO I, A, DA LEI COMPLEMENTAR Nº 173/2020, DESTINADOS A AÇÕES DE ENFRENTAMENTO À COVID-19, A SEREM APLICADOS EM AÇÕES DE SAÚDE E ASSISTÊNCIA SOCIAL.</t>
+  </si>
+  <si>
+    <t>RECURSOS DE DESVINCULAÇÃO DE RECEITAS - EC 93/2016</t>
+  </si>
+  <si>
+    <t>FUNDO DE MANUTENCAO E DESENVOLVIMENTO DA EDUCACAO BÁSICA - FUNDEB - REGULARIZAÇÃO DE EXERCÍCIOS ANTERIORES</t>
+  </si>
+  <si>
+    <t>CONTROLE DOS RECURSOS NÃO VINCULADOS PROVENIENTES DA COMPENSAÇÃO DE IMPOSTOS PARA ATENDIMENTO AO DISPOSTO NO ARTIGO 9º DA LC 141/2012</t>
+  </si>
+  <si>
+    <t>EXPLORAÇÃO E PRODUÇÃO DE PETRÓLEO  E GÁS NATURAL</t>
+  </si>
+  <si>
+    <t>TRANSFERÊNCIAS DO FNDE VINCULADOS À EDUCAÇÃO - EXCETO EMENDAS INDIVIDUAIS E DE BANCADA</t>
+  </si>
+  <si>
+    <t>TRANSFERÊNCIAS DA UNIÃO VINCULADOS À SAÚDE</t>
+  </si>
+  <si>
+    <t>RECURSOS VINCULADOS AO PAGAMENTO DOS BENEFÍCIOS CONCEDIDOS NA FORMA DO ART. 38, OBSERVADO O DISPOSTO NOS ARTS. 39 E 50 DA LEI COMPLEMENTAR Nº 64, DE 25/03/2002.</t>
+  </si>
+  <si>
+    <t>RECURSOS VINCULADOS AO PAGAMENTO DOS BENEFÍCIOS CONCEDIDOS NA FORMA DO ART. 38, OBSERVADO O DISPOSTO NOS ARTS. 39 E 50 DA LEI COMPLEMENTAR Nº 64, DE 25/03/2002</t>
+  </si>
+  <si>
+    <t>DOAÇÕES DE PESSOAS FÍSICAS OU JURÍDICAS, DE INSTITUIÇÕES PRIVADAS OU DO EXTERIOR A ÓRGÃO E ENTIDADES DO ESTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECURSOS RECEBIDOS COMO DOAÇÕES A ÓRGÃO E ENTIDADES DO ESTADO REALIZADAS POR PESSOAS FÍSICAS, INSTITUIÇÕES PRIVADAS NACIONAIS OU ENTIDADES INTERNACIONAIS, QUE NÃO SEJAM DECORRENTES DE TERMOS DE AJUSTAMENTO DE CONDUTA, DOAÇÕES COM VINCULAÇÃO POR INSTRUMENTO JURÍDICO E CONGÊNERES.
+</t>
+  </si>
+  <si>
+    <t>DOAÇÕES DE PESSOAS FÍSICAS OU JURÍDICAS, DE INSTITUIÇÕES PRIVADAS OU DO EXTERIOR AO TESOURO ESTADUAL</t>
+  </si>
+  <si>
+    <t>RECURSOS RECEBIDOS COMO DOAÇÕES AO TESOURO ESTADUAL REALIZADAS POR PESSOAS FÍSICAS, INSTITUIÇÕES PRIVADAS NACIONAIS OU ENTIDADES INTERNACIONAIS, QUE NÃO SEJAM DECORRENTES DE TERMOS DE AJUSTAMENTO DE CONDUTA, DOAÇÕES COM VINCULAÇÃO POR INSTRUMENTO JURÍDICO E CONGÊNERES.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALIENAÇÃO DE BENS DO TESOURO ESTADUAL </t>
+  </si>
+  <si>
+    <t>TRANSFERÊNCIAS DOS MUNICÍPIOS VINCULADOS À FARMÁCIA BÁSICA - FES</t>
+  </si>
+  <si>
+    <t>RECURSOS VINCULADOS A ÓRGÃOS E ENTIDADES DA ADMINISTRAÇÃO DIRETA E INDIRETA ATRAVÉS DE LEGISLAÇÃO ESPECÍFICA, QUE NÃO SE ENQUADRAM NOS ITENS ANTERIORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECURSOS QUE TÊM ORIGEM NO ESFORÇO PRÓPRIO DE ARRECADAÇÃO DE ÓRGÃOS E ENTIDADES DA ADMINISTRAÇÃO DIRETA E INDIRETA. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACORDOS E AJUSTES DE COOPERAÇÃO MÚTUA COM A UNIÃO E SUAS ENTIDADES. </t>
+  </si>
+  <si>
+    <t>RECURSOS DECORRENTES DA CONVERSÃO DE MULTAS AMBIENTAIS</t>
+  </si>
+  <si>
+    <t>RECURSOS DECORRENTES DA CONVERSÃO DE MULTAS AMBIENTAIS, A QUE SE REFEREM O § 6° DO ART. 16 DA LEI Nº 7.772, DE 8 DE SETEMBRO DE 1980, O § 6º DO ART. 20 DA LEI Nº 14.181, DE 17 DE JANEIRO DE 2002, E O ART. 106-A DA LEI Nº 20.922, DE 16 DE OUTUBRO DE 2013.</t>
+  </si>
+  <si>
+    <t>RECURSOS DE DEPÓSITOS JUDICIAIS LEI 21.720/15</t>
+  </si>
+  <si>
+    <t>RECURSOS DO FUNDO DE EQUALIZAÇÃO FEDERATIVA – FEF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+BÔNUS DE ASSINATURA DO EXCEDENTE DA CESSÃO ONEROSA PELA EXPLORAÇÃO DO PRÉ-SAL
+</t>
+  </si>
+  <si>
+    <t>AUXÍLIO FINANCEIRO RECEBIDO DA UNIÃO PARA APLICAÇÃO EM AÇÕES DE ENFRENTAMENTO AO CORONAVÍRUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -676,7 +747,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -685,11 +756,43 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -964,16 +1067,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultColWidth="55.42578125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I100"/>
+  <sheetFormatPr defaultColWidth="55.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="61" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -984,7 +1091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -994,8 +1101,29 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4">
+        <f>IF(A2=D2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H2" s="4">
+        <f>IF(B2=E2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I2" s="4">
+        <f>IF(C2=F2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1005,8 +1133,29 @@
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="4">
+        <f>IF(A3=D3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="4">
+        <f>IF(B3=E3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <f>IF(C3=F3,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1016,8 +1165,29 @@
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="4">
+        <f>IF(A4=D4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <f>IF(B4=E4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <f>IF(C4=F4,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1027,8 +1197,29 @@
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4">
+        <f>IF(A5=D5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="4">
+        <f>IF(B5=E5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="4">
+        <f>IF(C5=F5,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1038,8 +1229,29 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4">
+        <f>IF(A6=D6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H6" s="4">
+        <f>IF(B6=E6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <f>IF(C6=F6,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1049,8 +1261,29 @@
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="4">
+        <f>IF(A7=D7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="4">
+        <f>IF(B7=E7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I7" s="4">
+        <f>IF(C7=F7,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1060,8 +1293,29 @@
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="4">
+        <f>IF(A8=D8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H8" s="4">
+        <f>IF(B8=E8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I8" s="4">
+        <f>IF(C8=F8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1071,8 +1325,29 @@
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="4">
+        <f>IF(A9=D9,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H9" s="4">
+        <f>IF(B9=E9,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="4">
+        <f>IF(C9=F9,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1082,8 +1357,29 @@
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="4">
+        <f>IF(A10=D10,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="4">
+        <f>IF(B10=E10,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="4">
+        <f>IF(C10=F10,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1093,8 +1389,29 @@
       <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="4">
+        <f>IF(A11=D11,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H11" s="4">
+        <f>IF(B11=E11,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I11" s="4">
+        <f>IF(C11=F11,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1104,8 +1421,29 @@
       <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="4">
+        <f>IF(A12=D12,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="4">
+        <f>IF(B12=E12,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
+        <f>IF(C12=F12,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1115,8 +1453,29 @@
       <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="4">
+        <f>IF(A13=D13,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <f>IF(B13=E13,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <f>IF(C13=F13,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1126,8 +1485,29 @@
       <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="4">
+        <f>IF(A14=D14,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <f>IF(B14=E14,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <f>IF(C14=F14,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1137,8 +1517,29 @@
       <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="4">
+        <f>IF(A15=D15,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="4">
+        <f>IF(B15=E15,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
+        <f>IF(C15=F15,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1148,8 +1549,29 @@
       <c r="C16" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="4">
+        <f>IF(A16=D16,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H16" s="4">
+        <f>IF(B16=E16,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I16" s="4">
+        <f>IF(C16=F16,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1159,8 +1581,29 @@
       <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="4">
+        <f>IF(A17=D17,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <f>IF(B17=E17,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I17" s="4">
+        <f>IF(C17=F17,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1170,8 +1613,29 @@
       <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="4">
+        <f>IF(A18=D18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H18" s="4">
+        <f>IF(B18=E18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I18" s="4">
+        <f>IF(C18=F18,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1181,8 +1645,29 @@
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="4">
+        <f>IF(A19=D19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H19" s="4">
+        <f>IF(B19=E19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I19" s="4">
+        <f>IF(C19=F19,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1192,8 +1677,29 @@
       <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" t="s">
+        <v>200</v>
+      </c>
+      <c r="G20" s="4">
+        <f>IF(A20=D20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H20" s="4">
+        <f>IF(B20=E20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I20" s="4">
+        <f>IF(C20=F20,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1203,8 +1709,29 @@
       <c r="C21" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="4">
+        <f>IF(A21=D21,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H21" s="4">
+        <f>IF(B21=E21,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I21" s="4">
+        <f>IF(C21=F21,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1214,8 +1741,29 @@
       <c r="C22" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="4">
+        <f>IF(A22=D22,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <f>IF(B22=E22,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I22" s="4">
+        <f>IF(C22=F22,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1225,8 +1773,29 @@
       <c r="C23" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="4">
+        <f>IF(A23=D23,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H23" s="4">
+        <f>IF(B23=E23,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I23" s="4">
+        <f>IF(C23=F23,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1236,8 +1805,29 @@
       <c r="C24" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="4">
+        <f>IF(A24=D24,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H24" s="4">
+        <f>IF(B24=E24,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I24" s="4">
+        <f>IF(C24=F24,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1247,8 +1837,29 @@
       <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="4">
+        <f>IF(A25=D25,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H25" s="4">
+        <f>IF(B25=E25,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I25" s="4">
+        <f>IF(C25=F25,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1258,8 +1869,29 @@
       <c r="C26" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="4">
+        <f>IF(A26=D26,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H26" s="4">
+        <f>IF(B26=E26,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I26" s="4">
+        <f>IF(C26=F26,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1269,8 +1901,29 @@
       <c r="C27" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27" s="4">
+        <f>IF(A27=D27,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H27" s="4">
+        <f>IF(B27=E27,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I27" s="4">
+        <f>IF(C27=F27,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1280,8 +1933,29 @@
       <c r="C28" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28" s="4">
+        <f>IF(A28=D28,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H28" s="4">
+        <f>IF(B28=E28,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I28" s="4">
+        <f>IF(C28=F28,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1291,8 +1965,29 @@
       <c r="C29" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" s="4">
+        <f>IF(A29=D29,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H29" s="4">
+        <f>IF(B29=E29,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I29" s="4">
+        <f>IF(C29=F29,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1302,8 +1997,29 @@
       <c r="C30" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30">
+        <v>29</v>
+      </c>
+      <c r="E30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="4">
+        <f>IF(A30=D30,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H30" s="4">
+        <f>IF(B30=E30,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I30" s="4">
+        <f>IF(C30=F30,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1313,8 +2029,29 @@
       <c r="C31" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" s="4">
+        <f>IF(A31=D31,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H31" s="4">
+        <f>IF(B31=E31,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I31" s="4">
+        <f>IF(C31=F31,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1324,8 +2061,29 @@
       <c r="C32" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="4">
+        <f>IF(A32=D32,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
+        <f>IF(B32=E32,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I32" s="4">
+        <f>IF(C32=F32,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1335,8 +2093,29 @@
       <c r="C33" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33" s="4">
+        <f>IF(A33=D33,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H33" s="4">
+        <f>IF(B33=E33,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I33" s="4">
+        <f>IF(C33=F33,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1346,8 +2125,29 @@
       <c r="C34" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>201</v>
+      </c>
+      <c r="F34" t="s">
+        <v>68</v>
+      </c>
+      <c r="G34" s="4">
+        <f>IF(A34=D34,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H34" s="4">
+        <f>IF(B34=E34,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="4">
+        <f>IF(C34=F34,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1357,8 +2157,29 @@
       <c r="C35" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35">
+        <v>34</v>
+      </c>
+      <c r="E35" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="4">
+        <f>IF(A35=D35,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H35" s="4">
+        <f>IF(B35=E35,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I35" s="4">
+        <f>IF(C35=F35,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1368,8 +2189,29 @@
       <c r="C36" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36">
+        <v>35</v>
+      </c>
+      <c r="E36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="4">
+        <f>IF(A36=D36,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H36" s="4">
+        <f>IF(B36=E36,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I36" s="4">
+        <f>IF(C36=F36,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1379,8 +2221,29 @@
       <c r="C37" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>202</v>
+      </c>
+      <c r="F37" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="4">
+        <f>IF(A37=D37,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H37" s="4">
+        <f>IF(B37=E37,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="4">
+        <f>IF(C37=F37,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1390,8 +2253,29 @@
       <c r="C38" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38">
+        <v>37</v>
+      </c>
+      <c r="E38" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="4">
+        <f>IF(A38=D38,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H38" s="4">
+        <f>IF(B38=E38,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="4">
+        <f>IF(C38=F38,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1401,8 +2285,29 @@
       <c r="C39" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39">
+        <v>38</v>
+      </c>
+      <c r="E39" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39" t="s">
+        <v>78</v>
+      </c>
+      <c r="G39" s="4">
+        <f>IF(A39=D39,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H39" s="4">
+        <f>IF(B39=E39,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I39" s="4">
+        <f>IF(C39=F39,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1412,8 +2317,29 @@
       <c r="C40" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40">
+        <v>39</v>
+      </c>
+      <c r="E40" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" s="4">
+        <f>IF(A40=D40,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H40" s="4">
+        <f>IF(B40=E40,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I40" s="4">
+        <f>IF(C40=F40,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1423,16 +2349,55 @@
       <c r="C41" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41">
+        <v>40</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="4">
+        <f>IF(A41=D41,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H41" s="4">
+        <f>IF(B41=E41,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I41" s="4">
+        <f>IF(C41=F41,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="D42">
+        <v>41</v>
+      </c>
+      <c r="E42" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" s="4">
+        <f>IF(A42=D42,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H42" s="4">
+        <f>IF(B42=E42,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I42" s="4">
+        <f>IF(C42=F42,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1442,8 +2407,29 @@
       <c r="C43" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="D43">
+        <v>42</v>
+      </c>
+      <c r="E43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F43" t="s">
+        <v>204</v>
+      </c>
+      <c r="G43" s="4">
+        <f>IF(A43=D43,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H43" s="4">
+        <f>IF(B43=E43,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I43" s="4">
+        <f>IF(C43=F43,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1453,8 +2439,29 @@
       <c r="C44" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="D44">
+        <v>43</v>
+      </c>
+      <c r="E44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" t="s">
+        <v>205</v>
+      </c>
+      <c r="G44" s="4">
+        <f>IF(A44=D44,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H44" s="4">
+        <f>IF(B44=E44,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I44" s="4">
+        <f>IF(C44=F44,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1464,8 +2471,29 @@
       <c r="C45" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="D45">
+        <v>44</v>
+      </c>
+      <c r="E45" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="4">
+        <f>IF(A45=D45,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H45" s="4">
+        <f>IF(B45=E45,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I45" s="4">
+        <f>IF(C45=F45,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1475,8 +2503,29 @@
       <c r="C46" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="D46">
+        <v>45</v>
+      </c>
+      <c r="E46" t="s">
+        <v>206</v>
+      </c>
+      <c r="F46" t="s">
+        <v>207</v>
+      </c>
+      <c r="G46" s="4">
+        <f>IF(A46=D46,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H46" s="4">
+        <f>IF(B46=E46,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="4">
+        <f>IF(C46=F46,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1486,8 +2535,29 @@
       <c r="C47" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="D47">
+        <v>46</v>
+      </c>
+      <c r="E47" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47" t="s">
+        <v>209</v>
+      </c>
+      <c r="G47" s="4">
+        <f>IF(A47=D47,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H47" s="4">
+        <f>IF(B47=E47,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="4">
+        <f>IF(C47=F47,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1497,8 +2567,29 @@
       <c r="C48" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="D48">
+        <v>47</v>
+      </c>
+      <c r="E48" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" t="s">
+        <v>93</v>
+      </c>
+      <c r="G48" s="4">
+        <f>IF(A48=D48,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H48" s="4">
+        <f>IF(B48=E48,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I48" s="4">
+        <f>IF(C48=F48,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1508,8 +2599,29 @@
       <c r="C49" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="D49">
+        <v>48</v>
+      </c>
+      <c r="E49" t="s">
+        <v>210</v>
+      </c>
+      <c r="F49" t="s">
+        <v>95</v>
+      </c>
+      <c r="G49" s="4">
+        <f>IF(A49=D49,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H49" s="4">
+        <f>IF(B49=E49,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="4">
+        <f>IF(C49=F49,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1519,8 +2631,29 @@
       <c r="C50" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="D50">
+        <v>49</v>
+      </c>
+      <c r="E50" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" t="s">
+        <v>97</v>
+      </c>
+      <c r="G50" s="4">
+        <f>IF(A50=D50,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H50" s="4">
+        <f>IF(B50=E50,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I50" s="4">
+        <f>IF(C50=F50,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1530,8 +2663,29 @@
       <c r="C51" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51">
+        <v>50</v>
+      </c>
+      <c r="E51" t="s">
+        <v>98</v>
+      </c>
+      <c r="F51" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" s="4">
+        <f>IF(A51=D51,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H51" s="4">
+        <f>IF(B51=E51,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I51" s="4">
+        <f>IF(C51=F51,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1541,8 +2695,29 @@
       <c r="C52" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52">
+        <v>51</v>
+      </c>
+      <c r="E52" t="s">
+        <v>100</v>
+      </c>
+      <c r="F52" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" s="4">
+        <f>IF(A52=D52,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H52" s="4">
+        <f>IF(B52=E52,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I52" s="4">
+        <f>IF(C52=F52,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1552,8 +2727,29 @@
       <c r="C53" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="D53">
+        <v>52</v>
+      </c>
+      <c r="E53" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" t="s">
+        <v>103</v>
+      </c>
+      <c r="G53" s="4">
+        <f>IF(A53=D53,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H53" s="4">
+        <f>IF(B53=E53,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I53" s="4">
+        <f>IF(C53=F53,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1563,8 +2759,29 @@
       <c r="C54" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="D54">
+        <v>53</v>
+      </c>
+      <c r="E54" t="s">
+        <v>104</v>
+      </c>
+      <c r="F54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G54" s="4">
+        <f>IF(A54=D54,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H54" s="4">
+        <f>IF(B54=E54,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I54" s="4">
+        <f>IF(C54=F54,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1574,8 +2791,29 @@
       <c r="C55" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="D55">
+        <v>54</v>
+      </c>
+      <c r="E55" t="s">
+        <v>106</v>
+      </c>
+      <c r="F55" t="s">
+        <v>107</v>
+      </c>
+      <c r="G55" s="4">
+        <f>IF(A55=D55,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H55" s="4">
+        <f>IF(B55=E55,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I55" s="4">
+        <f>IF(C55=F55,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1585,8 +2823,29 @@
       <c r="C56" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="D56">
+        <v>55</v>
+      </c>
+      <c r="E56" t="s">
+        <v>211</v>
+      </c>
+      <c r="F56" t="s">
+        <v>109</v>
+      </c>
+      <c r="G56" s="4">
+        <f>IF(A56=D56,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H56" s="4">
+        <f>IF(B56=E56,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="4">
+        <f>IF(C56=F56,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1596,8 +2855,29 @@
       <c r="C57" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="D57">
+        <v>56</v>
+      </c>
+      <c r="E57" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57" t="s">
+        <v>111</v>
+      </c>
+      <c r="G57" s="4">
+        <f>IF(A57=D57,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H57" s="4">
+        <f>IF(B57=E57,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I57" s="4">
+        <f>IF(C57=F57,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1607,8 +2887,29 @@
       <c r="C58" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58">
+        <v>57</v>
+      </c>
+      <c r="E58" t="s">
+        <v>112</v>
+      </c>
+      <c r="F58" t="s">
+        <v>113</v>
+      </c>
+      <c r="G58" s="4">
+        <f>IF(A58=D58,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H58" s="4">
+        <f>IF(B58=E58,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I58" s="4">
+        <f>IF(C58=F58,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1618,8 +2919,29 @@
       <c r="C59" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="D59">
+        <v>58</v>
+      </c>
+      <c r="E59" t="s">
+        <v>114</v>
+      </c>
+      <c r="F59" t="s">
+        <v>115</v>
+      </c>
+      <c r="G59" s="4">
+        <f>IF(A59=D59,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H59" s="4">
+        <f>IF(B59=E59,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I59" s="4">
+        <f>IF(C59=F59,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1629,8 +2951,29 @@
       <c r="C60" s="1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="D60">
+        <v>59</v>
+      </c>
+      <c r="E60" t="s">
+        <v>116</v>
+      </c>
+      <c r="F60" t="s">
+        <v>212</v>
+      </c>
+      <c r="G60" s="4">
+        <f>IF(A60=D60,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H60" s="4">
+        <f>IF(B60=E60,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I60" s="4">
+        <f>IF(C60=F60,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1640,8 +2983,29 @@
       <c r="C61" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="D61">
+        <v>60</v>
+      </c>
+      <c r="E61" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" t="s">
+        <v>213</v>
+      </c>
+      <c r="G61" s="4">
+        <f>IF(A61=D61,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H61" s="4">
+        <f>IF(B61=E61,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I61" s="4">
+        <f>IF(C61=F61,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1651,8 +3015,29 @@
       <c r="C62" s="1" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="D62">
+        <v>61</v>
+      </c>
+      <c r="E62" t="s">
+        <v>120</v>
+      </c>
+      <c r="F62" t="s">
+        <v>121</v>
+      </c>
+      <c r="G62" s="4">
+        <f>IF(A62=D62,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H62" s="4">
+        <f>IF(B62=E62,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I62" s="4">
+        <f>IF(C62=F62,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1662,8 +3047,29 @@
       <c r="C63" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="D63">
+        <v>62</v>
+      </c>
+      <c r="E63" t="s">
+        <v>122</v>
+      </c>
+      <c r="F63" t="s">
+        <v>123</v>
+      </c>
+      <c r="G63" s="4">
+        <f>IF(A63=D63,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H63" s="4">
+        <f>IF(B63=E63,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I63" s="4">
+        <f>IF(C63=F63,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1673,8 +3079,29 @@
       <c r="C64" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="D64">
+        <v>63</v>
+      </c>
+      <c r="E64" t="s">
+        <v>124</v>
+      </c>
+      <c r="F64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G64" s="4">
+        <f>IF(A64=D64,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H64" s="4">
+        <f>IF(B64=E64,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I64" s="4">
+        <f>IF(C64=F64,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1684,8 +3111,29 @@
       <c r="C65" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65">
+        <v>64</v>
+      </c>
+      <c r="E65" t="s">
+        <v>126</v>
+      </c>
+      <c r="F65" t="s">
+        <v>127</v>
+      </c>
+      <c r="G65" s="4">
+        <f>IF(A65=D65,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H65" s="4">
+        <f>IF(B65=E65,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I65" s="4">
+        <f>IF(C65=F65,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1695,8 +3143,29 @@
       <c r="C66" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66">
+        <v>65</v>
+      </c>
+      <c r="E66" t="s">
+        <v>128</v>
+      </c>
+      <c r="F66" t="s">
+        <v>129</v>
+      </c>
+      <c r="G66" s="4">
+        <f>IF(A66=D66,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H66" s="4">
+        <f>IF(B66=E66,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I66" s="4">
+        <f>IF(C66=F66,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1706,8 +3175,29 @@
       <c r="C67" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67">
+        <v>66</v>
+      </c>
+      <c r="E67" t="s">
+        <v>130</v>
+      </c>
+      <c r="F67" t="s">
+        <v>131</v>
+      </c>
+      <c r="G67" s="4">
+        <f>IF(A67=D67,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H67" s="4">
+        <f>IF(B67=E67,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I67" s="4">
+        <f>IF(C67=F67,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1717,8 +3207,29 @@
       <c r="C68" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="D68">
+        <v>67</v>
+      </c>
+      <c r="E68" t="s">
+        <v>132</v>
+      </c>
+      <c r="F68" t="s">
+        <v>133</v>
+      </c>
+      <c r="G68" s="4">
+        <f>IF(A68=D68,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H68" s="4">
+        <f>IF(B68=E68,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I68" s="4">
+        <f>IF(C68=F68,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1728,8 +3239,29 @@
       <c r="C69" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="D69">
+        <v>68</v>
+      </c>
+      <c r="E69" t="s">
+        <v>134</v>
+      </c>
+      <c r="F69" t="s">
+        <v>135</v>
+      </c>
+      <c r="G69" s="4">
+        <f>IF(A69=D69,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H69" s="4">
+        <f>IF(B69=E69,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I69" s="4">
+        <f>IF(C69=F69,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1739,8 +3271,29 @@
       <c r="C70" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="D70">
+        <v>69</v>
+      </c>
+      <c r="E70" t="s">
+        <v>136</v>
+      </c>
+      <c r="F70" t="s">
+        <v>137</v>
+      </c>
+      <c r="G70" s="4">
+        <f>IF(A70=D70,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H70" s="4">
+        <f>IF(B70=E70,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I70" s="4">
+        <f>IF(C70=F70,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1750,8 +3303,29 @@
       <c r="C71" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="D71">
+        <v>70</v>
+      </c>
+      <c r="E71" t="s">
+        <v>138</v>
+      </c>
+      <c r="F71" t="s">
+        <v>139</v>
+      </c>
+      <c r="G71" s="4">
+        <f>IF(A71=D71,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H71" s="4">
+        <f>IF(B71=E71,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I71" s="4">
+        <f>IF(C71=F71,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1761,8 +3335,29 @@
       <c r="C72" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="D72">
+        <v>71</v>
+      </c>
+      <c r="E72" t="s">
+        <v>140</v>
+      </c>
+      <c r="F72" t="s">
+        <v>141</v>
+      </c>
+      <c r="G72" s="4">
+        <f>IF(A72=D72,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H72" s="4">
+        <f>IF(B72=E72,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I72" s="4">
+        <f>IF(C72=F72,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1772,8 +3367,29 @@
       <c r="C73" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="D73">
+        <v>72</v>
+      </c>
+      <c r="E73" t="s">
+        <v>142</v>
+      </c>
+      <c r="F73" t="s">
+        <v>143</v>
+      </c>
+      <c r="G73" s="4">
+        <f>IF(A73=D73,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H73" s="4">
+        <f>IF(B73=E73,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I73" s="4">
+        <f>IF(C73=F73,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1783,8 +3399,29 @@
       <c r="C74" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="D74">
+        <v>73</v>
+      </c>
+      <c r="E74" t="s">
+        <v>214</v>
+      </c>
+      <c r="F74" t="s">
+        <v>145</v>
+      </c>
+      <c r="G74" s="4">
+        <f>IF(A74=D74,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H74" s="4">
+        <f>IF(B74=E74,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I74" s="4">
+        <f>IF(C74=F74,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1794,8 +3431,29 @@
       <c r="C75" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="D75">
+        <v>74</v>
+      </c>
+      <c r="E75" t="s">
+        <v>146</v>
+      </c>
+      <c r="F75" t="s">
+        <v>147</v>
+      </c>
+      <c r="G75" s="4">
+        <f>IF(A75=D75,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H75" s="4">
+        <f>IF(B75=E75,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I75" s="4">
+        <f>IF(C75=F75,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1805,8 +3463,29 @@
       <c r="C76" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="D76">
+        <v>75</v>
+      </c>
+      <c r="E76" t="s">
+        <v>148</v>
+      </c>
+      <c r="F76" t="s">
+        <v>149</v>
+      </c>
+      <c r="G76" s="4">
+        <f>IF(A76=D76,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H76" s="4">
+        <f>IF(B76=E76,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I76" s="4">
+        <f>IF(C76=F76,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1816,8 +3495,29 @@
       <c r="C77" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="D77">
+        <v>76</v>
+      </c>
+      <c r="E77" t="s">
+        <v>150</v>
+      </c>
+      <c r="F77" t="s">
+        <v>151</v>
+      </c>
+      <c r="G77" s="4">
+        <f>IF(A77=D77,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H77" s="4">
+        <f>IF(B77=E77,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I77" s="4">
+        <f>IF(C77=F77,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1827,8 +3527,29 @@
       <c r="C78" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="D78">
+        <v>77</v>
+      </c>
+      <c r="E78" t="s">
+        <v>152</v>
+      </c>
+      <c r="F78" t="s">
+        <v>153</v>
+      </c>
+      <c r="G78" s="4">
+        <f>IF(A78=D78,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H78" s="4">
+        <f>IF(B78=E78,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I78" s="4">
+        <f>IF(C78=F78,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1838,8 +3559,29 @@
       <c r="C79" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="D79">
+        <v>78</v>
+      </c>
+      <c r="E79" t="s">
+        <v>154</v>
+      </c>
+      <c r="F79" t="s">
+        <v>155</v>
+      </c>
+      <c r="G79" s="4">
+        <f>IF(A79=D79,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H79" s="4">
+        <f>IF(B79=E79,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I79" s="4">
+        <f>IF(C79=F79,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1849,8 +3591,29 @@
       <c r="C80" s="1" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="D80">
+        <v>79</v>
+      </c>
+      <c r="E80" t="s">
+        <v>215</v>
+      </c>
+      <c r="F80" t="s">
+        <v>216</v>
+      </c>
+      <c r="G80" s="4">
+        <f>IF(A80=D80,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H80" s="4">
+        <f>IF(B80=E80,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I80" s="4">
+        <f>IF(C80=F80,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1860,8 +3623,29 @@
       <c r="C81" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81">
+        <v>80</v>
+      </c>
+      <c r="E81" t="s">
+        <v>158</v>
+      </c>
+      <c r="F81" t="s">
+        <v>159</v>
+      </c>
+      <c r="G81" s="4">
+        <f>IF(A81=D81,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H81" s="4">
+        <f>IF(B81=E81,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I81" s="4">
+        <f>IF(C81=F81,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1871,8 +3655,29 @@
       <c r="C82" s="1" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="D82">
+        <v>81</v>
+      </c>
+      <c r="E82" t="s">
+        <v>217</v>
+      </c>
+      <c r="F82" t="s">
+        <v>161</v>
+      </c>
+      <c r="G82" s="4">
+        <f>IF(A82=D82,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H82" s="4">
+        <f>IF(B82=E82,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="4">
+        <f>IF(C82=F82,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1882,8 +3687,29 @@
       <c r="C83" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="D83">
+        <v>82</v>
+      </c>
+      <c r="E83" t="s">
+        <v>162</v>
+      </c>
+      <c r="F83" t="s">
+        <v>163</v>
+      </c>
+      <c r="G83" s="4">
+        <f>IF(A83=D83,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H83" s="4">
+        <f>IF(B83=E83,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I83" s="4">
+        <f>IF(C83=F83,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1893,8 +3719,29 @@
       <c r="C84" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="D84">
+        <v>83</v>
+      </c>
+      <c r="E84" t="s">
+        <v>164</v>
+      </c>
+      <c r="F84" t="s">
+        <v>165</v>
+      </c>
+      <c r="G84" s="4">
+        <f>IF(A84=D84,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H84" s="4">
+        <f>IF(B84=E84,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I84" s="4">
+        <f>IF(C84=F84,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1904,8 +3751,29 @@
       <c r="C85" s="1" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="D85">
+        <v>84</v>
+      </c>
+      <c r="E85" t="s">
+        <v>166</v>
+      </c>
+      <c r="F85" t="s">
+        <v>167</v>
+      </c>
+      <c r="G85" s="4">
+        <f>IF(A85=D85,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H85" s="4">
+        <f>IF(B85=E85,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I85" s="4">
+        <f>IF(C85=F85,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1915,8 +3783,29 @@
       <c r="C86" s="1" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="D86">
+        <v>85</v>
+      </c>
+      <c r="E86" t="s">
+        <v>168</v>
+      </c>
+      <c r="F86" t="s">
+        <v>169</v>
+      </c>
+      <c r="G86" s="4">
+        <f>IF(A86=D86,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H86" s="4">
+        <f>IF(B86=E86,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I86" s="4">
+        <f>IF(C86=F86,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1926,8 +3815,29 @@
       <c r="C87" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="D87">
+        <v>86</v>
+      </c>
+      <c r="E87" t="s">
+        <v>170</v>
+      </c>
+      <c r="F87" t="s">
+        <v>171</v>
+      </c>
+      <c r="G87" s="4">
+        <f>IF(A87=D87,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H87" s="4">
+        <f>IF(B87=E87,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I87" s="4">
+        <f>IF(C87=F87,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -1937,8 +3847,29 @@
       <c r="C88" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="D88">
+        <v>87</v>
+      </c>
+      <c r="E88" t="s">
+        <v>172</v>
+      </c>
+      <c r="F88" t="s">
+        <v>173</v>
+      </c>
+      <c r="G88" s="4">
+        <f>IF(A88=D88,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H88" s="4">
+        <f>IF(B88=E88,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I88" s="4">
+        <f>IF(C88=F88,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -1948,8 +3879,29 @@
       <c r="C89" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="D89">
+        <v>88</v>
+      </c>
+      <c r="E89" t="s">
+        <v>174</v>
+      </c>
+      <c r="F89" t="s">
+        <v>175</v>
+      </c>
+      <c r="G89" s="4">
+        <f>IF(A89=D89,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H89" s="4">
+        <f>IF(B89=E89,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I89" s="4">
+        <f>IF(C89=F89,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -1959,8 +3911,29 @@
       <c r="C90" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="D90">
+        <v>89</v>
+      </c>
+      <c r="E90" t="s">
+        <v>218</v>
+      </c>
+      <c r="F90" t="s">
+        <v>177</v>
+      </c>
+      <c r="G90" s="4">
+        <f>IF(A90=D90,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H90" s="4">
+        <f>IF(B90=E90,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I90" s="4">
+        <f>IF(C90=F90,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -1970,8 +3943,29 @@
       <c r="C91" s="1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="D91">
+        <v>90</v>
+      </c>
+      <c r="E91" t="s">
+        <v>178</v>
+      </c>
+      <c r="F91" t="s">
+        <v>179</v>
+      </c>
+      <c r="G91" s="4">
+        <f>IF(A91=D91,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H91" s="4">
+        <f>IF(B91=E91,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I91" s="4">
+        <f>IF(C91=F91,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -1981,8 +3975,29 @@
       <c r="C92" s="1" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="D92">
+        <v>91</v>
+      </c>
+      <c r="E92" t="s">
+        <v>180</v>
+      </c>
+      <c r="F92" t="s">
+        <v>181</v>
+      </c>
+      <c r="G92" s="4">
+        <f>IF(A92=D92,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H92" s="4">
+        <f>IF(B92=E92,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I92" s="4">
+        <f>IF(C92=F92,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -1992,8 +4007,29 @@
       <c r="C93" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="D93">
+        <v>92</v>
+      </c>
+      <c r="E93" t="s">
+        <v>182</v>
+      </c>
+      <c r="F93" t="s">
+        <v>183</v>
+      </c>
+      <c r="G93" s="4">
+        <f>IF(A93=D93,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H93" s="4">
+        <f>IF(B93=E93,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I93" s="4">
+        <f>IF(C93=F93,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2003,8 +4039,29 @@
       <c r="C94" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="D94">
+        <v>93</v>
+      </c>
+      <c r="E94" t="s">
+        <v>184</v>
+      </c>
+      <c r="F94" t="s">
+        <v>185</v>
+      </c>
+      <c r="G94" s="4">
+        <f>IF(A94=D94,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H94" s="4">
+        <f>IF(B94=E94,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I94" s="4">
+        <f>IF(C94=F94,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2014,8 +4071,29 @@
       <c r="C95" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="D95">
+        <v>94</v>
+      </c>
+      <c r="E95" t="s">
+        <v>186</v>
+      </c>
+      <c r="F95" t="s">
+        <v>187</v>
+      </c>
+      <c r="G95" s="4">
+        <f>IF(A95=D95,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H95" s="4">
+        <f>IF(B95=E95,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I95" s="4">
+        <f>IF(C95=F95,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2025,8 +4103,29 @@
       <c r="C96" s="1" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="D96">
+        <v>95</v>
+      </c>
+      <c r="E96" t="s">
+        <v>188</v>
+      </c>
+      <c r="F96" t="s">
+        <v>189</v>
+      </c>
+      <c r="G96" s="4">
+        <f>IF(A96=D96,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H96" s="4">
+        <f>IF(B96=E96,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I96" s="4">
+        <f>IF(C96=F96,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2036,8 +4135,29 @@
       <c r="C97" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="D97">
+        <v>96</v>
+      </c>
+      <c r="E97" t="s">
+        <v>219</v>
+      </c>
+      <c r="F97" t="s">
+        <v>191</v>
+      </c>
+      <c r="G97" s="4">
+        <f>IF(A97=D97,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H97" s="4">
+        <f>IF(B97=E97,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I97" s="4">
+        <f>IF(C97=F97,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2047,8 +4167,29 @@
       <c r="C98" s="1" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="D98">
+        <v>97</v>
+      </c>
+      <c r="E98" t="s">
+        <v>192</v>
+      </c>
+      <c r="F98" t="s">
+        <v>193</v>
+      </c>
+      <c r="G98" s="4">
+        <f>IF(A98=D98,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H98" s="4">
+        <f>IF(B98=E98,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I98" s="4">
+        <f>IF(C98=F98,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2058,8 +4199,29 @@
       <c r="C99" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
+      <c r="D99">
+        <v>98</v>
+      </c>
+      <c r="E99" t="s">
+        <v>194</v>
+      </c>
+      <c r="F99" t="s">
+        <v>195</v>
+      </c>
+      <c r="G99" s="4">
+        <f>IF(A99=D99,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H99" s="4">
+        <f>IF(B99=E99,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I99" s="4">
+        <f>IF(C99=F99,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2069,25 +4231,78 @@
       <c r="C100" s="1" t="s">
         <v>197</v>
       </c>
+      <c r="D100">
+        <v>99</v>
+      </c>
+      <c r="E100" t="s">
+        <v>220</v>
+      </c>
+      <c r="F100" t="s">
+        <v>197</v>
+      </c>
+      <c r="G100" s="4">
+        <f>IF(A100=D100,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H100" s="4">
+        <f>IF(B100=E100,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I100" s="4">
+        <f>IF(C100=F100,1,0)</f>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G2:I100">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <UserInfo>
+        <DisplayName>Sofia Chacon Furletti (SEPLAG)</DisplayName>
+        <AccountId>70</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Rodolfo Pinhón Bechtlufft (SEPLAG)</DisplayName>
+        <AccountId>38</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Carlos Henrique de Oliveira Brochado (SEPLAG)</DisplayName>
+        <AccountId>49</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Carolina Fonseca Moreira (SEPLAG)</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -2347,46 +4562,54 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
-      <UserInfo>
-        <DisplayName>Sofia Chacon Furletti (SEPLAG)</DisplayName>
-        <AccountId>70</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Rodolfo Pinhón Bechtlufft (SEPLAG)</DisplayName>
-        <AccountId>38</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Carlos Henrique de Oliveira Brochado (SEPLAG)</DisplayName>
-        <AccountId>49</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Carolina Fonseca Moreira (SEPLAG)</DisplayName>
-        <AccountId>13</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52695D42-7905-4355-AFA3-D66DFF9609E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{741C4EED-4E68-4D13-8A53-EE95607C61BA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC3FA630-D18C-4B56-A359-9CD6CF90D85A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9398F535-E0C5-40FC-A458-15A5F4068865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{741C4EED-4E68-4D13-8A53-EE95607C61BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52695D42-7905-4355-AFA3-D66DFF9609E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data-raw/desc_fontes_de_recursos.xlsx
+++ b/data-raw/desc_fontes_de_recursos.xlsx
@@ -994,7 +994,7 @@
     <col min="3" max="3" style="7" width="61.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C42" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
       <c r="A51" s="3">
         <v>50</v>
       </c>

--- a/data-raw/desc_fontes_de_recursos.xlsx
+++ b/data-raw/desc_fontes_de_recursos.xlsx
@@ -994,7 +994,7 @@
     <col min="3" max="3" style="7" width="61.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C42" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3">
         <v>50</v>
       </c>

--- a/data-raw/desc_fontes_de_recursos.xlsx
+++ b/data-raw/desc_fontes_de_recursos.xlsx
@@ -1,19 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19350" windowHeight="7965"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Plan1"/>
+    <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Plan1!$A$1:$C$100</definedName>
-    <definedName name="LOCAL_MYSQL_DATE_FORMAT">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$C$100</definedName>
+    <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -488,12 +509,6 @@
     <t xml:space="preserve">CONTRIBUIÇÃO SOBRE A TOTALIDADE DA REMUNERAÇÃO DOS MILITARES ATIVOS, INATIVOS E PENSIONISTAS, DESTINADA AO CUSTEIO DAS PENSÕES E INATIVIDADE DOS MILITARES – LEI 13.954/2019 </t>
   </si>
   <si>
-    <t>CONTRIBUIÇÃO PATRONAL PARA O FUNPREV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECURSOS ADVINDOS DE CONTRIBUIÇÃO PATRONAL, VINCULADOS AO PAGAMENTO DOS BENEFÍCIOS CONCEDIDOS NA FORMA DO ART. 3º DA LEI COMPLEMENTAR Nº 132/2014. </t>
-  </si>
-  <si>
     <t>RECURSOS DO ACORDO DE REPACTUAÇÃO DO RIO DOCE</t>
   </si>
   <si>
@@ -527,7 +542,7 @@
     <t>TRANSFERÊNCIAS DO SUS PARA A VIGILÂNCIA EM SAÚDE</t>
   </si>
   <si>
-    <t xml:space="preserve">RECURSOS TRANSFERIDOS PARA FINANCIAMENTO DE AÇÕES DE VIGILÂNCIA EM SAÚDE, CONFORME DISPÕE A PORTARIA N° 204/GM, DE 29/01/2007, DO MINISTÉRIO DA SAÚDE. </t>
+    <t>RECURSOS TRANSFERIDOS PARA FINANCIAMENTO DE AÇÕES DE VIGILÂNCIA EM SAÚDE, CONFORME DISPÕE A PORTARIA N° 204/GM, DE 29/01/2007, DO MINISTÉRIO DA SAÚDE. </t>
   </si>
   <si>
     <t>TRANSFERÊNCIAS DO SUS PARA A ASSISTÊNCIA FARMACÊUTICA</t>
@@ -612,13 +627,18 @@
   </si>
   <si>
     <t>RECURSOS PREVISTOS NO ART. 5º, INCISO I, A, DA LEI COMPLEMENTAR Nº 173/2020, DESTINADOS A AÇÕES DE ENFRENTAMENTO À COVID-19, A SEREM APLICADOS EM AÇÕES DE SAÚDE E ASSISTÊNCIA SOCIAL.</t>
+  </si>
+  <si>
+    <t>RECURSOS DECORRENTES DA CONVERSÃO DE MULTAS AMBIENTAIS</t>
+  </si>
+  <si>
+    <t>RECURSOS DECORRENTES DA CONVERSÃO DE MULTAS AMBIENTAIS, A QUE SE REFEREM O § 6° DO ART. 16 DA LEI Nº 7.772, DE 8 DE SETEMBRO DE 1980, O § 6º DO ART. 20 DA LEI Nº 14.181, DE 17 DE JANEIRO DE 2002, E O ART. 106-A DA LEI Nº 20.922, DE 16 DE OUTUBRO DE 2013.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -632,6 +652,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -642,14 +663,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -661,52 +675,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Escritório">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -733,85 +736,85 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Escritório">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Escritório">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -820,1279 +823,1601 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
-            </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="55.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="8.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="58.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="61.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="61" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="3">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C80" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="3">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="3">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="3">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
-      <c r="A84" s="3">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
-      <c r="A85" s="3">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
-      <c r="A86" s="3">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
-      <c r="A87" s="3">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
-      <c r="A88" s="3">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
-      <c r="A89" s="3">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
-      <c r="A90" s="3">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="3">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
-      <c r="A92" s="3">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
-      <c r="A93" s="3">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="3">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
-      <c r="A95" s="3">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="3">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
-      <c r="A97" s="3">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
-      <c r="A98" s="3">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
-      <c r="A99" s="3">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
-      <c r="A100" s="3">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <UserInfo>
+        <DisplayName>Sofia Chacon Furletti (SEPLAG)</DisplayName>
+        <AccountId>70</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Rodolfo Pinhón Bechtlufft (SEPLAG)</DisplayName>
+        <AccountId>38</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Carlos Henrique de Oliveira Brochado (SEPLAG)</DisplayName>
+        <AccountId>49</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Carolina Fonseca Moreira (SEPLAG)</DisplayName>
+        <AccountId>13</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
+    <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6f4338ef-addb-4c87-aefe-1895241b335f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="917d32f3-4fa4-4f5b-a8d0-62dbd3d265b9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="21" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="22" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{98708050-f001-4dcd-9fe1-c60e835c33fc}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{741C4EED-4E68-4D13-8A53-EE95607C61BA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52695D42-7905-4355-AFA3-D66DFF9609E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9398F535-E0C5-40FC-A458-15A5F4068865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>